--- a/Legacy_version/RANAS Analyser v1.0.1 (Legacy).xlsx
+++ b/Legacy_version/RANAS Analyser v1.0.1 (Legacy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tdhch-my.sharepoint.com/personal/sebastien_mercier_tdh_ch/Documents/Gravit'eau/RANAS/RANAS Analyser/Current published versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17701" documentId="8_{0D220551-2BE6-4D46-A044-3A706D0A2BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72994127-B91F-45DF-A92C-6E4A46A8CF26}"/>
+  <xr:revisionPtr revIDLastSave="17704" documentId="8_{0D220551-2BE6-4D46-A044-3A706D0A2BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60D00361-0AD6-4649-8FD9-E772E8A5BEE3}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="-18120" windowWidth="24240" windowHeight="17520" tabRatio="697" firstSheet="2" activeTab="2" xr2:uid="{85543DA6-F95A-4457-9F61-0C74C53DF323}"/>
   </bookViews>
@@ -128,7 +128,7 @@
     <definedName name="yesLabel" comment="Reference to the label meaning &quot;yes&quot; in the drop-down menus of the &quot;Include?&quot; and &quot;Display?&quot; columns of the &quot;Behaviour&quot; and &quot;Factors&quot; configuration tables.  Used in UI text and conditional formatting rules.">INDEX(yesNoTable[label], MATCH("yes", yesNoTable[tag], 0))</definedName>
     <definedName name="yesNoList" comment="List of yes/no values (check mark/cross mark) used in drop-down menus in the &quot;Behaviour configuration table&quot; and &quot;Factors configuration table&quot; to include behaviour questions/factors in the behaviour score/analysis chart.">yesNoTable[label]</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -11308,9 +11308,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange2</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -11355,9 +11355,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange2</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -11402,9 +11402,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange2</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -11771,9 +11771,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange1</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -11905,9 +11905,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange1</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -12039,9 +12039,9 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>[0]!chartFactorRange1</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -16215,9 +16215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>853440</xdr:colOff>
+      <xdr:colOff>857250</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>365397</xdr:rowOff>
+      <xdr:rowOff>361587</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16545,7 +16545,7 @@
                   <a14:compatExt spid="_x0000_s10243"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -45969,19 +45969,21 @@
       <c r="F22" s="62"/>
       <c r="G22" s="224"/>
       <c r="H22" s="217" t="str">
-        <f>IFERROR(
-    INDEX(
+        <f>HYPERLINK(
+    IFERROR(
       INDEX(
-        UITranslationTable[],
-        0,
-        IFERROR(
-          MATCH(UILanguage, UITranslationTable[#Headers], 0),
-          MATCH("English", UITranslationTable[#Headers], 0)
-        )
-      ),
-      MATCH("introLicenseLink", UITranslationTable[tag], 0)
-    ),#REF!
-  ) &amp; ""</f>
+        INDEX(
+          UITranslationTable[],
+          0,
+          IFERROR(
+            MATCH(UILanguage, UITranslationTable[#Headers], 0),
+            MATCH("English", UITranslationTable[#Headers], 0)
+          )
+        ),
+        MATCH("introLicenseLink", UITranslationTable[tag], 0)
+      ),#REF!
+    ) &amp; ""
+  )</f>
         <v>https://creativecommons.org/licenses/by-nc-nd/4.0/</v>
       </c>
       <c r="I22" s="218"/>
@@ -46004,7 +46006,7 @@
       <c r="L23" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a6UFH2YUNoLayhZXqUndwi8l0gyr4tcp6/9n2tXyGeEAsfBUXBmj78fZNxUq71FONdm0hG8lM2JMMvouMRTszA==" saltValue="AN2XTQftlrkqMmvef+NFdA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="29AZnfm4Q19JJOkr8TnWc3XR6ymheyD8TJ7i98Zd7CSytDtpFPJbD5Q7n67eAHU2JeIEycjCBxsLzn4KEM+Ppg==" saltValue="XlrQkobJddGacnQLB6dQMw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="18">
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
